--- a/data/nzd0567/nzd0567.xlsx
+++ b/data/nzd0567/nzd0567.xlsx
@@ -13242,7 +13242,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B951"/>
+  <dimension ref="A1:B952"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22755,6 +22755,16 @@
       </c>
       <c r="B951" t="n">
         <v>1.36</v>
+      </c>
+    </row>
+    <row r="952">
+      <c r="A952" t="inlineStr">
+        <is>
+          <t>2025-11-30 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B952" t="n">
+        <v>-0.73</v>
       </c>
     </row>
   </sheetData>

--- a/data/nzd0567/nzd0567.xlsx
+++ b/data/nzd0567/nzd0567.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D711"/>
+  <dimension ref="A1:D713"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13226,6 +13226,42 @@
         <v>228.05</v>
       </c>
       <c r="D711" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:07:30+00:00</t>
+        </is>
+      </c>
+      <c r="B712" t="n">
+        <v>276.42</v>
+      </c>
+      <c r="C712" t="n">
+        <v>227.87</v>
+      </c>
+      <c r="D712" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-16 22:07:36+00:00</t>
+        </is>
+      </c>
+      <c r="B713" t="n">
+        <v>276.69</v>
+      </c>
+      <c r="C713" t="n">
+        <v>227.31</v>
+      </c>
+      <c r="D713" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -13242,7 +13278,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B952"/>
+  <dimension ref="A1:B954"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22765,6 +22801,26 @@
       </c>
       <c r="B952" t="n">
         <v>-0.73</v>
+      </c>
+    </row>
+    <row r="953">
+      <c r="A953" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B953" t="n">
+        <v>0.41</v>
+      </c>
+    </row>
+    <row r="954">
+      <c r="A954" t="inlineStr">
+        <is>
+          <t>2025-12-16 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B954" t="n">
+        <v>0.36</v>
       </c>
     </row>
   </sheetData>
@@ -22927,28 +22983,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1854870410361864</v>
+        <v>0.1855182179882382</v>
       </c>
       <c r="J2" t="n">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="K2" t="n">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="L2" t="n">
-        <v>0.07702451412960332</v>
+        <v>0.07753245774250517</v>
       </c>
       <c r="M2" t="n">
-        <v>4.137144596311479</v>
+        <v>4.125906303175032</v>
       </c>
       <c r="N2" t="n">
-        <v>23.61629040292496</v>
+        <v>23.55001182557808</v>
       </c>
       <c r="O2" t="n">
-        <v>4.859659494545371</v>
+        <v>4.852835441839964</v>
       </c>
       <c r="P2" t="n">
-        <v>271.5920984756815</v>
+        <v>271.5917925622999</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -22999,28 +23055,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1385748265537743</v>
+        <v>0.1387741530253655</v>
       </c>
       <c r="J3" t="n">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="K3" t="n">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="L3" t="n">
-        <v>0.137091795674953</v>
+        <v>0.1382309123444019</v>
       </c>
       <c r="M3" t="n">
-        <v>2.167171235841489</v>
+        <v>2.162058889508235</v>
       </c>
       <c r="N3" t="n">
-        <v>6.896881818248761</v>
+        <v>6.878037529694117</v>
       </c>
       <c r="O3" t="n">
-        <v>2.626191504488726</v>
+        <v>2.622601290645247</v>
       </c>
       <c r="P3" t="n">
-        <v>223.5762289794299</v>
+        <v>223.5742699578315</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -23058,7 +23114,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D711"/>
+  <dimension ref="A1:D713"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38699,6 +38755,50 @@
         </is>
       </c>
     </row>
+    <row r="712">
+      <c r="A712" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:07:30+00:00</t>
+        </is>
+      </c>
+      <c r="B712" t="inlineStr">
+        <is>
+          <t>-41.03322597718262,173.02270129345513</t>
+        </is>
+      </c>
+      <c r="C712" t="inlineStr">
+        <is>
+          <t>-41.03292633214222,173.0217112213717</t>
+        </is>
+      </c>
+      <c r="D712" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-16 22:07:36+00:00</t>
+        </is>
+      </c>
+      <c r="B713" t="inlineStr">
+        <is>
+          <t>-41.03322449318922,173.0227038383124</t>
+        </is>
+      </c>
+      <c r="C713" t="inlineStr">
+        <is>
+          <t>-41.03292900556435,173.02170557189532</t>
+        </is>
+      </c>
+      <c r="D713" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0567/nzd0567.xlsx
+++ b/data/nzd0567/nzd0567.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D713"/>
+  <dimension ref="A1:D714"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13262,6 +13262,24 @@
         <v>227.31</v>
       </c>
       <c r="D713" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-17 22:07:34+00:00</t>
+        </is>
+      </c>
+      <c r="B714" t="n">
+        <v>275.21</v>
+      </c>
+      <c r="C714" t="n">
+        <v>226.86</v>
+      </c>
+      <c r="D714" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -13278,7 +13296,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B954"/>
+  <dimension ref="A1:B955"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22821,6 +22839,16 @@
       </c>
       <c r="B954" t="n">
         <v>0.36</v>
+      </c>
+    </row>
+    <row r="955">
+      <c r="A955" t="inlineStr">
+        <is>
+          <t>2026-01-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B955" t="n">
+        <v>1.25</v>
       </c>
     </row>
   </sheetData>
@@ -22983,28 +23011,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1855182179882382</v>
+        <v>0.1851426408521271</v>
       </c>
       <c r="J2" t="n">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="K2" t="n">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="L2" t="n">
-        <v>0.07753245774250517</v>
+        <v>0.07747998448177496</v>
       </c>
       <c r="M2" t="n">
-        <v>4.125906303175032</v>
+        <v>4.121893135090055</v>
       </c>
       <c r="N2" t="n">
-        <v>23.55001182557808</v>
+        <v>23.51935509547698</v>
       </c>
       <c r="O2" t="n">
-        <v>4.852835441839964</v>
+        <v>4.849675772201373</v>
       </c>
       <c r="P2" t="n">
-        <v>271.5917925622999</v>
+        <v>271.595488814176</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -23055,28 +23083,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1387741530253655</v>
+        <v>0.1386595237292665</v>
       </c>
       <c r="J3" t="n">
+        <v>713</v>
+      </c>
+      <c r="K3" t="n">
         <v>712</v>
       </c>
-      <c r="K3" t="n">
-        <v>711</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.1382309123444019</v>
+        <v>0.1384384953002892</v>
       </c>
       <c r="M3" t="n">
-        <v>2.162058889508235</v>
+        <v>2.159571026473529</v>
       </c>
       <c r="N3" t="n">
-        <v>6.878037529694117</v>
+        <v>6.868597137189655</v>
       </c>
       <c r="O3" t="n">
-        <v>2.622601290645247</v>
+        <v>2.620800857980181</v>
       </c>
       <c r="P3" t="n">
-        <v>223.5742699578315</v>
+        <v>223.5754016448762</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -23114,7 +23142,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D713"/>
+  <dimension ref="A1:D714"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38799,6 +38827,28 @@
         </is>
       </c>
     </row>
+    <row r="714">
+      <c r="A714" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-17 22:07:34+00:00</t>
+        </is>
+      </c>
+      <c r="B714" t="inlineStr">
+        <is>
+          <t>-41.03323262767077,173.022689888723</t>
+        </is>
+      </c>
+      <c r="C714" t="inlineStr">
+        <is>
+          <t>-41.03293115384978,173.0217010321372</t>
+        </is>
+      </c>
+      <c r="D714" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0567/nzd0567.xlsx
+++ b/data/nzd0567/nzd0567.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D714"/>
+  <dimension ref="A1:D718"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13280,6 +13280,78 @@
         <v>226.86</v>
       </c>
       <c r="D714" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-25 22:07:19+00:00</t>
+        </is>
+      </c>
+      <c r="B715" t="n">
+        <v>273.79</v>
+      </c>
+      <c r="C715" t="n">
+        <v>225.88</v>
+      </c>
+      <c r="D715" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-01 22:13:28+00:00</t>
+        </is>
+      </c>
+      <c r="B716" t="n">
+        <v>272.84</v>
+      </c>
+      <c r="C716" t="n">
+        <v>225.56</v>
+      </c>
+      <c r="D716" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:07:14+00:00</t>
+        </is>
+      </c>
+      <c r="B717" t="n">
+        <v>271.16</v>
+      </c>
+      <c r="C717" t="n">
+        <v>224.61</v>
+      </c>
+      <c r="D717" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-18 22:07:22+00:00</t>
+        </is>
+      </c>
+      <c r="B718" t="n">
+        <v>271.85</v>
+      </c>
+      <c r="C718" t="n">
+        <v>224.87</v>
+      </c>
+      <c r="D718" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -13296,7 +13368,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B955"/>
+  <dimension ref="A1:B959"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22849,6 +22921,46 @@
       </c>
       <c r="B955" t="n">
         <v>1.25</v>
+      </c>
+    </row>
+    <row r="956">
+      <c r="A956" t="inlineStr">
+        <is>
+          <t>2026-01-25 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B956" t="n">
+        <v>-0.86</v>
+      </c>
+    </row>
+    <row r="957">
+      <c r="A957" t="inlineStr">
+        <is>
+          <t>2026-02-01 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B957" t="n">
+        <v>1.78</v>
+      </c>
+    </row>
+    <row r="958">
+      <c r="A958" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B958" t="n">
+        <v>-0.59</v>
+      </c>
+    </row>
+    <row r="959">
+      <c r="A959" t="inlineStr">
+        <is>
+          <t>2026-02-18 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B959" t="n">
+        <v>1.72</v>
       </c>
     </row>
   </sheetData>
@@ -23011,28 +23123,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1851426408521271</v>
+        <v>0.1804743865768121</v>
       </c>
       <c r="J2" t="n">
-        <v>713</v>
+        <v>717</v>
       </c>
       <c r="K2" t="n">
-        <v>713</v>
+        <v>717</v>
       </c>
       <c r="L2" t="n">
-        <v>0.07747998448177496</v>
+        <v>0.07455402478401763</v>
       </c>
       <c r="M2" t="n">
-        <v>4.121893135090055</v>
+        <v>4.120712655950527</v>
       </c>
       <c r="N2" t="n">
-        <v>23.51935509547698</v>
+        <v>23.48611066058144</v>
       </c>
       <c r="O2" t="n">
-        <v>4.849675772201373</v>
+        <v>4.846247069700578</v>
       </c>
       <c r="P2" t="n">
-        <v>271.595488814176</v>
+        <v>271.64154476793</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -23083,28 +23195,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1386595237292665</v>
+        <v>0.136341020890158</v>
       </c>
       <c r="J3" t="n">
-        <v>713</v>
+        <v>717</v>
       </c>
       <c r="K3" t="n">
-        <v>712</v>
+        <v>716</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1384384953002892</v>
+        <v>0.1356435083946377</v>
       </c>
       <c r="M3" t="n">
-        <v>2.159571026473529</v>
+        <v>2.158491013728514</v>
       </c>
       <c r="N3" t="n">
-        <v>6.868597137189655</v>
+        <v>6.85436310784027</v>
       </c>
       <c r="O3" t="n">
-        <v>2.620800857980181</v>
+        <v>2.618083861880721</v>
       </c>
       <c r="P3" t="n">
-        <v>223.5754016448762</v>
+        <v>223.5983478805603</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -23142,7 +23254,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D714"/>
+  <dimension ref="A1:D718"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38849,6 +38961,94 @@
         </is>
       </c>
     </row>
+    <row r="715">
+      <c r="A715" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-25 22:07:19+00:00</t>
+        </is>
+      </c>
+      <c r="B715" t="inlineStr">
+        <is>
+          <t>-41.03324043237445,173.02267650465427</t>
+        </is>
+      </c>
+      <c r="C715" t="inlineStr">
+        <is>
+          <t>-41.03293583233746,173.0216911455518</t>
+        </is>
+      </c>
+      <c r="D715" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-01 22:13:28+00:00</t>
+        </is>
+      </c>
+      <c r="B716" t="inlineStr">
+        <is>
+          <t>-41.03324565383027,173.02266755052204</t>
+        </is>
+      </c>
+      <c r="C716" t="inlineStr">
+        <is>
+          <t>-41.03293736000671,173.02168791727874</t>
+        </is>
+      </c>
+      <c r="D716" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:07:14+00:00</t>
+        </is>
+      </c>
+      <c r="B717" t="inlineStr">
+        <is>
+          <t>-41.03325488756094,173.0226517158426</t>
+        </is>
+      </c>
+      <c r="C717" t="inlineStr">
+        <is>
+          <t>-41.03294189527429,173.02167833334215</t>
+        </is>
+      </c>
+      <c r="D717" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-18 22:07:22+00:00</t>
+        </is>
+      </c>
+      <c r="B718" t="inlineStr">
+        <is>
+          <t>-41.0332510951361,173.0226582193722</t>
+        </is>
+      </c>
+      <c r="C718" t="inlineStr">
+        <is>
+          <t>-41.032940654043244,173.0216809563144</t>
+        </is>
+      </c>
+      <c r="D718" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0567/nzd0567.xlsx
+++ b/data/nzd0567/nzd0567.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D718"/>
+  <dimension ref="A1:D722"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13352,6 +13352,78 @@
         <v>224.87</v>
       </c>
       <c r="D718" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:13:19+00:00</t>
+        </is>
+      </c>
+      <c r="B719" t="n">
+        <v>271</v>
+      </c>
+      <c r="C719" t="n">
+        <v>224.89</v>
+      </c>
+      <c r="D719" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-06 22:07:20+00:00</t>
+        </is>
+      </c>
+      <c r="B720" t="n">
+        <v>271.5</v>
+      </c>
+      <c r="C720" t="n">
+        <v>225.15</v>
+      </c>
+      <c r="D720" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:13:25+00:00</t>
+        </is>
+      </c>
+      <c r="B721" t="n">
+        <v>271.03</v>
+      </c>
+      <c r="C721" t="n">
+        <v>224.92</v>
+      </c>
+      <c r="D721" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-22 22:07:09+00:00</t>
+        </is>
+      </c>
+      <c r="B722" t="n">
+        <v>271.1</v>
+      </c>
+      <c r="C722" t="n">
+        <v>225.03</v>
+      </c>
+      <c r="D722" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -13368,7 +13440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B959"/>
+  <dimension ref="A1:B963"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22961,6 +23033,46 @@
       </c>
       <c r="B959" t="n">
         <v>1.72</v>
+      </c>
+    </row>
+    <row r="960">
+      <c r="A960" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B960" t="n">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="961">
+      <c r="A961" t="inlineStr">
+        <is>
+          <t>2026-03-06 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B961" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="962">
+      <c r="A962" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B962" t="n">
+        <v>-0.26</v>
+      </c>
+    </row>
+    <row r="963">
+      <c r="A963" t="inlineStr">
+        <is>
+          <t>2026-03-22 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B963" t="n">
+        <v>0.67</v>
       </c>
     </row>
   </sheetData>
@@ -23123,28 +23235,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1804743865768121</v>
+        <v>0.1745216123396721</v>
       </c>
       <c r="J2" t="n">
-        <v>717</v>
+        <v>721</v>
       </c>
       <c r="K2" t="n">
-        <v>717</v>
+        <v>721</v>
       </c>
       <c r="L2" t="n">
-        <v>0.07455402478401763</v>
+        <v>0.07050870434141365</v>
       </c>
       <c r="M2" t="n">
-        <v>4.120712655950527</v>
+        <v>4.125785500287948</v>
       </c>
       <c r="N2" t="n">
-        <v>23.48611066058144</v>
+        <v>23.50902764133112</v>
       </c>
       <c r="O2" t="n">
-        <v>4.846247069700578</v>
+        <v>4.848610898116194</v>
       </c>
       <c r="P2" t="n">
-        <v>271.64154476793</v>
+        <v>271.7004882975744</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -23195,28 +23307,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.136341020890158</v>
+        <v>0.1338158417327197</v>
       </c>
       <c r="J3" t="n">
-        <v>717</v>
+        <v>721</v>
       </c>
       <c r="K3" t="n">
-        <v>716</v>
+        <v>720</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1356435083946377</v>
+        <v>0.1324040756275731</v>
       </c>
       <c r="M3" t="n">
-        <v>2.158491013728514</v>
+        <v>2.158431517365372</v>
       </c>
       <c r="N3" t="n">
-        <v>6.85436310784027</v>
+        <v>6.84371716873445</v>
       </c>
       <c r="O3" t="n">
-        <v>2.618083861880721</v>
+        <v>2.616049917095324</v>
       </c>
       <c r="P3" t="n">
-        <v>223.5983478805603</v>
+        <v>223.6234299681282</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -23254,7 +23366,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D718"/>
+  <dimension ref="A1:D722"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39049,6 +39161,94 @@
         </is>
       </c>
     </row>
+    <row r="719">
+      <c r="A719" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:13:19+00:00</t>
+        </is>
+      </c>
+      <c r="B719" t="inlineStr">
+        <is>
+          <t>-41.033255766963755,173.02265020777767</t>
+        </is>
+      </c>
+      <c r="C719" t="inlineStr">
+        <is>
+          <t>-41.03294055856393,173.02168115808152</t>
+        </is>
+      </c>
+      <c r="D719" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-06 22:07:20+00:00</t>
+        </is>
+      </c>
+      <c r="B720" t="inlineStr">
+        <is>
+          <t>-41.03325301882992,173.02265492048045</t>
+        </is>
+      </c>
+      <c r="C720" t="inlineStr">
+        <is>
+          <t>-41.032939317332826,173.02168378105364</t>
+        </is>
+      </c>
+      <c r="D720" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:13:25+00:00</t>
+        </is>
+      </c>
+      <c r="B721" t="inlineStr">
+        <is>
+          <t>-41.03325560207573,173.02265049053983</t>
+        </is>
+      </c>
+      <c r="C721" t="inlineStr">
+        <is>
+          <t>-41.03294041534496,173.02168146073214</t>
+        </is>
+      </c>
+      <c r="D721" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-22 22:07:09+00:00</t>
+        </is>
+      </c>
+      <c r="B722" t="inlineStr">
+        <is>
+          <t>-41.033255217337,173.02265115031827</t>
+        </is>
+      </c>
+      <c r="C722" t="inlineStr">
+        <is>
+          <t>-41.03293989020872,173.0216825704511</t>
+        </is>
+      </c>
+      <c r="D722" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0567/nzd0567.xlsx
+++ b/data/nzd0567/nzd0567.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D722"/>
+  <dimension ref="A1:D726"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13426,6 +13426,78 @@
       <c r="D722" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:12:55+00:00</t>
+        </is>
+      </c>
+      <c r="B723" t="n">
+        <v>271.16</v>
+      </c>
+      <c r="C723" t="n">
+        <v>224.84</v>
+      </c>
+      <c r="D723" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-30 22:06:52+00:00</t>
+        </is>
+      </c>
+      <c r="B724" t="n">
+        <v>271.67</v>
+      </c>
+      <c r="C724" t="n">
+        <v>224.8</v>
+      </c>
+      <c r="D724" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:13:11+00:00</t>
+        </is>
+      </c>
+      <c r="B725" t="n">
+        <v>271.46</v>
+      </c>
+      <c r="C725" t="n">
+        <v>224.58</v>
+      </c>
+      <c r="D725" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-15 22:06:47+00:00</t>
+        </is>
+      </c>
+      <c r="B726" t="n">
+        <v>271.97</v>
+      </c>
+      <c r="C726" t="n">
+        <v>224.76</v>
+      </c>
+      <c r="D726" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -13440,7 +13512,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B963"/>
+  <dimension ref="A1:B969"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23073,6 +23145,66 @@
       </c>
       <c r="B963" t="n">
         <v>0.67</v>
+      </c>
+    </row>
+    <row r="964">
+      <c r="A964" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B964" t="n">
+        <v>0.54</v>
+      </c>
+    </row>
+    <row r="965">
+      <c r="A965" t="inlineStr">
+        <is>
+          <t>2026-03-30 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B965" t="n">
+        <v>1.07</v>
+      </c>
+    </row>
+    <row r="966">
+      <c r="A966" t="inlineStr">
+        <is>
+          <t>2026-04-07 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B966" t="n">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="967">
+      <c r="A967" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B967" t="n">
+        <v>0.62</v>
+      </c>
+    </row>
+    <row r="968">
+      <c r="A968" t="inlineStr">
+        <is>
+          <t>2026-04-15 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B968" t="n">
+        <v>1.21</v>
+      </c>
+    </row>
+    <row r="969">
+      <c r="A969" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B969" t="n">
+        <v>-0.82</v>
       </c>
     </row>
   </sheetData>
@@ -23235,28 +23367,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1745216123396721</v>
+        <v>0.1691978399047729</v>
       </c>
       <c r="J2" t="n">
-        <v>721</v>
+        <v>725</v>
       </c>
       <c r="K2" t="n">
-        <v>721</v>
+        <v>725</v>
       </c>
       <c r="L2" t="n">
-        <v>0.07050870434141365</v>
+        <v>0.06705035401167936</v>
       </c>
       <c r="M2" t="n">
-        <v>4.125785500287948</v>
+        <v>4.128111895204972</v>
       </c>
       <c r="N2" t="n">
-        <v>23.50902764133112</v>
+        <v>23.50470198612906</v>
       </c>
       <c r="O2" t="n">
-        <v>4.848610898116194</v>
+        <v>4.848164805999179</v>
       </c>
       <c r="P2" t="n">
-        <v>271.7004882975744</v>
+        <v>271.7533584796136</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -23307,28 +23439,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1338158417327197</v>
+        <v>0.1310815068021996</v>
       </c>
       <c r="J3" t="n">
-        <v>721</v>
+        <v>725</v>
       </c>
       <c r="K3" t="n">
-        <v>720</v>
+        <v>724</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1324040756275731</v>
+        <v>0.1286843199214385</v>
       </c>
       <c r="M3" t="n">
-        <v>2.158431517365372</v>
+        <v>2.159365009526698</v>
       </c>
       <c r="N3" t="n">
-        <v>6.84371716873445</v>
+        <v>6.838719381673418</v>
       </c>
       <c r="O3" t="n">
-        <v>2.616049917095324</v>
+        <v>2.615094526336174</v>
       </c>
       <c r="P3" t="n">
-        <v>223.6234299681282</v>
+        <v>223.6506709623077</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -23366,7 +23498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D722"/>
+  <dimension ref="A1:D726"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39249,6 +39381,94 @@
         </is>
       </c>
     </row>
+    <row r="723">
+      <c r="A723" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:12:55+00:00</t>
+        </is>
+      </c>
+      <c r="B723" t="inlineStr">
+        <is>
+          <t>-41.03325488756094,173.0226517158426</t>
+        </is>
+      </c>
+      <c r="C723" t="inlineStr">
+        <is>
+          <t>-41.03294079726221,173.02168065366376</t>
+        </is>
+      </c>
+      <c r="D723" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-30 22:06:52+00:00</t>
+        </is>
+      </c>
+      <c r="B724" t="inlineStr">
+        <is>
+          <t>-41.033252084464365,173.0226565227993</t>
+        </is>
+      </c>
+      <c r="C724" t="inlineStr">
+        <is>
+          <t>-41.032940988220844,173.02168025012958</t>
+        </is>
+      </c>
+      <c r="D724" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:13:11+00:00</t>
+        </is>
+      </c>
+      <c r="B725" t="inlineStr">
+        <is>
+          <t>-41.03325323868062,173.02265454346423</t>
+        </is>
+      </c>
+      <c r="C725" t="inlineStr">
+        <is>
+          <t>-41.03294203849325,173.0216780306915</t>
+        </is>
+      </c>
+      <c r="D725" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-15 22:06:47+00:00</t>
+        </is>
+      </c>
+      <c r="B726" t="inlineStr">
+        <is>
+          <t>-41.03325043558393,173.02265935042075</t>
+        </is>
+      </c>
+      <c r="C726" t="inlineStr">
+        <is>
+          <t>-41.032941179179474,173.0216798465954</t>
+        </is>
+      </c>
+      <c r="D726" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0567/nzd0567.xlsx
+++ b/data/nzd0567/nzd0567.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D726"/>
+  <dimension ref="A1:D729"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13496,6 +13496,60 @@
         <v>224.76</v>
       </c>
       <c r="D726" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:12:42+00:00</t>
+        </is>
+      </c>
+      <c r="B727" t="n">
+        <v>272.99</v>
+      </c>
+      <c r="C727" t="n">
+        <v>224.68</v>
+      </c>
+      <c r="D727" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:06:41+00:00</t>
+        </is>
+      </c>
+      <c r="B728" t="n">
+        <v>273.52</v>
+      </c>
+      <c r="C728" t="n">
+        <v>225</v>
+      </c>
+      <c r="D728" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:06:20+00:00</t>
+        </is>
+      </c>
+      <c r="B729" t="n">
+        <v>274.69</v>
+      </c>
+      <c r="C729" t="n">
+        <v>225.36</v>
+      </c>
+      <c r="D729" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -13512,7 +13566,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B969"/>
+  <dimension ref="A1:B973"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23205,6 +23259,46 @@
       </c>
       <c r="B969" t="n">
         <v>-0.82</v>
+      </c>
+    </row>
+    <row r="970">
+      <c r="A970" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B970" t="n">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="971">
+      <c r="A971" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B971" t="n">
+        <v>1.53</v>
+      </c>
+    </row>
+    <row r="972">
+      <c r="A972" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B972" t="n">
+        <v>-0.74</v>
+      </c>
+    </row>
+    <row r="973">
+      <c r="A973" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B973" t="n">
+        <v>1.81</v>
       </c>
     </row>
   </sheetData>
@@ -23367,28 +23461,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1691978399047729</v>
+        <v>0.167082874884516</v>
       </c>
       <c r="J2" t="n">
-        <v>725</v>
+        <v>728</v>
       </c>
       <c r="K2" t="n">
-        <v>725</v>
+        <v>728</v>
       </c>
       <c r="L2" t="n">
-        <v>0.06705035401167936</v>
+        <v>0.06602646254132816</v>
       </c>
       <c r="M2" t="n">
-        <v>4.128111895204972</v>
+        <v>4.120995673870619</v>
       </c>
       <c r="N2" t="n">
-        <v>23.50470198612906</v>
+        <v>23.43660531376429</v>
       </c>
       <c r="O2" t="n">
-        <v>4.848164805999179</v>
+        <v>4.841136779080331</v>
       </c>
       <c r="P2" t="n">
-        <v>271.7533584796136</v>
+        <v>271.7744289585017</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -23439,28 +23533,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1310815068021996</v>
+        <v>0.1292961200654657</v>
       </c>
       <c r="J3" t="n">
-        <v>725</v>
+        <v>728</v>
       </c>
       <c r="K3" t="n">
-        <v>724</v>
+        <v>727</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1286843199214385</v>
+        <v>0.1264218998444916</v>
       </c>
       <c r="M3" t="n">
-        <v>2.159365009526698</v>
+        <v>2.158895790512585</v>
       </c>
       <c r="N3" t="n">
-        <v>6.838719381673418</v>
+        <v>6.829734070220018</v>
       </c>
       <c r="O3" t="n">
-        <v>2.615094526336174</v>
+        <v>2.613375990977957</v>
       </c>
       <c r="P3" t="n">
-        <v>223.6506709623077</v>
+        <v>223.6685157471404</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -23498,7 +23592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D726"/>
+  <dimension ref="A1:D729"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39469,6 +39563,72 @@
         </is>
       </c>
     </row>
+    <row r="727">
+      <c r="A727" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:12:42+00:00</t>
+        </is>
+      </c>
+      <c r="B727" t="inlineStr">
+        <is>
+          <t>-41.03324482938993,173.0226689643325</t>
+        </is>
+      </c>
+      <c r="C727" t="inlineStr">
+        <is>
+          <t>-41.032941561096706,173.02167903952702</t>
+        </is>
+      </c>
+      <c r="D727" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:06:41+00:00</t>
+        </is>
+      </c>
+      <c r="B728" t="inlineStr">
+        <is>
+          <t>-41.033241916367224,173.02267395979578</t>
+        </is>
+      </c>
+      <c r="C728" t="inlineStr">
+        <is>
+          <t>-41.03294003342771,173.02168226780051</t>
+        </is>
+      </c>
+      <c r="D728" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:06:20+00:00</t>
+        </is>
+      </c>
+      <c r="B729" t="inlineStr">
+        <is>
+          <t>-41.03323548573145,173.0226849875151</t>
+        </is>
+      </c>
+      <c r="C729" t="inlineStr">
+        <is>
+          <t>-41.032938314799964,173.021685899608</t>
+        </is>
+      </c>
+      <c r="D729" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0567/nzd0567.xlsx
+++ b/data/nzd0567/nzd0567.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D729"/>
+  <dimension ref="A1:D730"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13550,6 +13550,24 @@
         <v>225.36</v>
       </c>
       <c r="D729" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-02 22:06:19+00:00</t>
+        </is>
+      </c>
+      <c r="B730" t="n">
+        <v>276.23</v>
+      </c>
+      <c r="C730" t="n">
+        <v>225.78</v>
+      </c>
+      <c r="D730" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -13566,7 +13584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B973"/>
+  <dimension ref="A1:B975"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23299,6 +23317,26 @@
       </c>
       <c r="B973" t="n">
         <v>1.81</v>
+      </c>
+    </row>
+    <row r="974">
+      <c r="A974" t="inlineStr">
+        <is>
+          <t>2026-06-02 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B974" t="n">
+        <v>1.03</v>
+      </c>
+    </row>
+    <row r="975">
+      <c r="A975" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B975" t="n">
+        <v>-0.82</v>
       </c>
     </row>
   </sheetData>
@@ -23461,28 +23499,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>0.167082874884516</v>
+        <v>0.1670709963621977</v>
       </c>
       <c r="J2" t="n">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="K2" t="n">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="L2" t="n">
-        <v>0.06602646254132816</v>
+        <v>0.06622152311485741</v>
       </c>
       <c r="M2" t="n">
-        <v>4.120995673870619</v>
+        <v>4.115397933740239</v>
       </c>
       <c r="N2" t="n">
-        <v>23.43660531376429</v>
+        <v>23.40445887275477</v>
       </c>
       <c r="O2" t="n">
-        <v>4.841136779080331</v>
+        <v>4.837815506274993</v>
       </c>
       <c r="P2" t="n">
-        <v>271.7744289585017</v>
+        <v>271.7745476939259</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -23533,28 +23571,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1292961200654657</v>
+        <v>0.128917165198425</v>
       </c>
       <c r="J3" t="n">
+        <v>729</v>
+      </c>
+      <c r="K3" t="n">
         <v>728</v>
       </c>
-      <c r="K3" t="n">
-        <v>727</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.1264218998444916</v>
+        <v>0.1260975622702389</v>
       </c>
       <c r="M3" t="n">
-        <v>2.158895790512585</v>
+        <v>2.157708730250934</v>
       </c>
       <c r="N3" t="n">
-        <v>6.829734070220018</v>
+        <v>6.822920778539673</v>
       </c>
       <c r="O3" t="n">
-        <v>2.613375990977957</v>
+        <v>2.612072123533283</v>
       </c>
       <c r="P3" t="n">
-        <v>223.6685157471404</v>
+        <v>223.6723154536824</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -23592,7 +23630,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D729"/>
+  <dimension ref="A1:D730"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39629,6 +39667,28 @@
         </is>
       </c>
     </row>
+    <row r="730">
+      <c r="A730" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-02 22:06:19+00:00</t>
+        </is>
+      </c>
+      <c r="B730" t="inlineStr">
+        <is>
+          <t>-41.03322702147421,173.0226995026296</t>
+        </is>
+      </c>
+      <c r="C730" t="inlineStr">
+        <is>
+          <t>-41.03293630973411,173.02169013671653</t>
+        </is>
+      </c>
+      <c r="D730" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
